--- a/reports/一级子公司A_现金流量表_2025-04.xlsx
+++ b/reports/一级子公司A_现金流量表_2025-04.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>148200000</v>
+        <v>147929539</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>557232000</v>
+        <v>555886703</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>2995931</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>11289315</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1499641</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>5618638</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>746684</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2820342</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>601433</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2249966</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>447148</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1689826</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>301018</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1126733</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>223577</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>843615</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>150355</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>564132</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>373355</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1404562</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>188408</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>709213</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>119074</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>446525</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>380000</v>
+        <v>379291</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1428800</v>
+        <v>1431746</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2700000</v>
+        <v>2708768</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>10152000</v>
+        <v>10136478</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>151280000</v>
+        <v>158664222</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>96000000</v>
+        <v>95652075</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>360960000</v>
+        <v>360238444</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1000732</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>3762804</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>748199</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2808580</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>498793</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1881310</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>375278</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1405056</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>248694</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>939732</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>189014</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>707065</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>15700000</v>
+        <v>15621958</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>59032000</v>
+        <v>59019929</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>8000000</v>
+        <v>8039065</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>30080000</v>
+        <v>30109311</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3300000</v>
+        <v>3285860</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>12408000</v>
+        <v>12387621</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>123000000</v>
+        <v>125659668</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>28280000</v>
+        <v>33004554</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>180000</v>
+        <v>179147</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>720000</v>
+        <v>720401</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1500000</v>
+        <v>1492888</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>6000000</v>
+        <v>5994037</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>920000</v>
+        <v>923669</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>3680000</v>
+        <v>3686089</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1680000</v>
+        <v>1672035</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14000000</v>
+        <v>14018918</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>56000000</v>
+        <v>56134691</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2000000</v>
+        <v>2000511</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>8000000</v>
+        <v>7980662</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10000000</v>
+        <v>9981645</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>40000000</v>
+        <v>40087063</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>380000</v>
+        <v>378110</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1520000</v>
+        <v>1519261</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14380000</v>
+        <v>14397028</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-12700000</v>
+        <v>-12724993</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3500000</v>
+        <v>3497083</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>14000000</v>
+        <v>13965877</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5500000</v>
+        <v>5512749</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>22000000</v>
+        <v>21954975</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5500000</v>
+        <v>5480141</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>22000000</v>
+        <v>22033296</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>180000</v>
+        <v>180815</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>720000</v>
+        <v>719408</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9180000</v>
+        <v>9190647</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4500000</v>
+        <v>4522003</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>18000000</v>
+        <v>18013269</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4500000</v>
+        <v>4480646</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>18000000</v>
+        <v>17974044</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>720000</v>
+        <v>722349</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>2880000</v>
+        <v>2885750</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>630000</v>
+        <v>630193</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>2520000</v>
+        <v>2526155</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>90000</v>
+        <v>90117</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>360000</v>
+        <v>359176</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5310000</v>
+        <v>5334469</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3870000</v>
+        <v>3856178</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>19450000</v>
+        <v>24135739</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>19450000</v>
+        <v>24135739</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
